--- a/data/trans_orig/Q5419_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar medios de transporte en 2023</t>
+          <t>Población según si es capaz de usar medios de transporte en 2023 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99496</t>
+          <t>99665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105744</t>
+          <t>105549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52233</t>
+          <t>52558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61316</t>
+          <t>61582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154745</t>
+          <t>154392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165541</t>
+          <t>165332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,62 +1560,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78445</t>
+          <t>79172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89122</t>
+          <t>89158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>35822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43134</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118124</t>
+          <t>117429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130002</t>
+          <t>130257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84048</t>
+          <t>84420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94262</t>
+          <t>94589</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30414</t>
+          <t>30916</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39943</t>
+          <t>40414</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118558</t>
+          <t>117684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132791</t>
+          <t>132435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>24714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26720</t>
+          <t>26985</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44945</t>
+          <t>44176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23606</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35885</t>
+          <t>34272</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>177757</t>
+          <t>176326</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>199333</t>
+          <t>198254</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>249954</t>
+          <t>249100</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>319743</t>
+          <t>320193</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>436912</t>
+          <t>439590</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>536358</t>
+          <t>535184</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>35061</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52647</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26578</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61755</t>
+          <t>61318</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>74217</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>120139</t>
+          <t>118540</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>137736</t>
+          <t>136909</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>185006</t>
+          <t>185465</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>208357</t>
+          <t>207811</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>28882</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>45753</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46310</t>
+          <t>47592</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>22496</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>39968</t>
+          <t>41196</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>41638</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>43146</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>44186</t>
+          <t>44276</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>190049</t>
+          <t>188653</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>213685</t>
+          <t>214916</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>189641</t>
+          <t>189077</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>214362</t>
+          <t>215711</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27616</t>
+          <t>27832</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>46502</t>
+          <t>46192</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>49348</t>
+          <t>45927</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>114889</t>
+          <t>114344</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>84853</t>
+          <t>80070</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>148933</t>
+          <t>147700</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>40793</t>
+          <t>40683</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>53256</t>
+          <t>53480</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>32071</t>
+          <t>31449</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>34490</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>84870</t>
+          <t>85492</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>107123</t>
+          <t>105693</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38288</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>95912</t>
+          <t>96723</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>67369</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>121475</t>
+          <t>121709</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>520834</t>
+          <t>521118</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>549833</t>
+          <t>550916</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>691092</t>
+          <t>692531</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>873092</t>
+          <t>875491</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1239435</t>
+          <t>1244498</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1415067</t>
+          <t>1422226</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5419_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Clase-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3846</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2973</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5407</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>553</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>103299</t>
+          <t>116002</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>112129</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105549</t>
+          <t>118614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>57685</t>
+          <t>66295</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52558</t>
+          <t>58999</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61582</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>160984</t>
+          <t>182298</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154392</t>
+          <t>174894</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165332</t>
+          <t>186964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1859,27 +1859,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>84734</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79172</t>
+          <t>86708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89158</t>
+          <t>98277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>47161</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35822</t>
+          <t>42268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>50536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>124865</t>
+          <t>141084</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117429</t>
+          <t>134010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130257</t>
+          <t>146853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>456</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>90277</t>
+          <t>100414</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84420</t>
+          <t>94766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94589</t>
+          <t>104376</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>38446</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30916</t>
+          <t>32536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40414</t>
+          <t>43457</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>125997</t>
+          <t>138860</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117684</t>
+          <t>130094</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>146309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24714</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>28092</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>36914</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,67 +3032,67 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>21130</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>14853</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>29401</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>7,52%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>19344</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>6254</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>33668</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>20173</t>
+          <t>21577</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34272</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>188608</t>
+          <t>207110</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>176326</t>
+          <t>196193</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>198254</t>
+          <t>218575</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>299438</t>
+          <t>101308</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>249100</t>
+          <t>94494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>320193</t>
+          <t>107542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>488046</t>
+          <t>308418</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>439590</t>
+          <t>295755</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>535184</t>
+          <t>320499</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>33779</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>43662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>42976</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35061</t>
+          <t>37289</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52240</t>
+          <t>55166</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26578</t>
+          <t>27864</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>35734</t>
+          <t>38265</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>68428</t>
+          <t>75905</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61318</t>
+          <t>68097</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>74217</t>
+          <t>81676</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>128321</t>
+          <t>137911</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>118540</t>
+          <t>127793</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>136909</t>
+          <t>148251</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>196749</t>
+          <t>213816</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>185465</t>
+          <t>200555</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>207811</t>
+          <t>225130</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>203760</t>
+          <t>218651</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>203760</t>
+          <t>218651</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>203760</t>
+          <t>218651</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>294908</t>
+          <t>318515</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>294908</t>
+          <t>318515</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>294908</t>
+          <t>318515</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>37017</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>32066</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>46188</t>
+          <t>51118</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>41785</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>33776</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47592</t>
+          <t>52111</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>15506</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>15506</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21861</t>
+          <t>23714</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,67 +4396,67 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>25225</t>
+          <t>27141</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>43624</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>35399</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>27360</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>45166</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t>7,85%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>33098</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>25862</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>41659</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>518</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>38226</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>27136</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>47816</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>35311</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>30704</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>44276</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>201304</t>
+          <t>215199</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>188653</t>
+          <t>201413</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>214916</t>
+          <t>228302</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>202363</t>
+          <t>216271</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>189077</t>
+          <t>201864</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>215711</t>
+          <t>229767</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>321145</t>
+          <t>345214</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>321145</t>
+          <t>345214</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>321145</t>
+          <t>345214</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>324349</t>
+          <t>348490</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>324349</t>
+          <t>348490</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>324349</t>
+          <t>348490</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,27 +4817,27 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>38848</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>29974</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>46192</t>
+          <t>50804</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>87582</t>
+          <t>94794</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>81327</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>114344</t>
+          <t>107685</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>124124</t>
+          <t>133642</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>80070</t>
+          <t>116861</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>147700</t>
+          <t>149995</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>23565</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>40683</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>41103</t>
+          <t>43652</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>34168</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>53480</t>
+          <t>55766</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>23102</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>31449</t>
+          <t>33953</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>64756</t>
+          <t>70187</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>34490</t>
+          <t>59445</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>85492</t>
+          <t>83562</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>87858</t>
+          <t>94945</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>81424</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>105693</t>
+          <t>111659</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>38288</t>
+          <t>39851</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>72551</t>
+          <t>79954</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>68710</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>96723</t>
+          <t>94419</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>101744</t>
+          <t>110406</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>67369</t>
+          <t>96111</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>121709</t>
+          <t>126077</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>594427</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>521118</t>
+          <t>577545</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>550916</t>
+          <t>608202</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>762599</t>
+          <t>606321</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>692531</t>
+          <t>584617</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>875491</t>
+          <t>626298</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1299004</t>
+          <t>1200748</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1244498</t>
+          <t>1174900</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1422226</t>
+          <t>1227680</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>637194</t>
+          <t>700733</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>637194</t>
+          <t>700733</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>637194</t>
+          <t>700733</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1016639</t>
+          <t>882660</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1016639</t>
+          <t>882660</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1016639</t>
+          <t>882660</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1653833</t>
+          <t>1583393</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1653833</t>
+          <t>1583393</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1653833</t>
+          <t>1583393</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
